--- a/scripts/example_input/voorbeeld_GD_Overslag.xlsx
+++ b/scripts/example_input/voorbeeld_GD_Overslag.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAKA\sources\github\faalkansbeheer\scripts\example_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D06E21B-D7CD-40A1-AFFB-9BD6AE32BF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CD5E60-C6BD-429B-878E-19596520F903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD979432-8D0D-462C-972B-AB828F23136F}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>Template:</t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>dierlijkegraverij</t>
+  </si>
+  <si>
+    <t>16-x</t>
+  </si>
+  <si>
+    <t>DP003</t>
   </si>
 </sst>
 </file>
@@ -977,9 +983,15 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+      <c r="A6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="6">
+        <v>250</v>
+      </c>
+      <c r="C6" s="6">
+        <v>350</v>
+      </c>
       <c r="D6" s="6">
         <v>1</v>
       </c>
@@ -999,10 +1011,14 @@
         <v>26</v>
       </c>
       <c r="J6" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
+        <v>300</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="M6" s="8" t="s">
         <v>29</v>
       </c>
@@ -4443,56 +4459,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document CB" ma:contentTypeID="0x010100A075C07AB76F2344B407AD577D6B92360100C7929242D85FED4E837C6D4097594A04" ma:contentTypeVersion="16" ma:contentTypeDescription="WSRL Document CB" ma:contentTypeScope="" ma:versionID="88fe53b6e98c5417adee0db248f913ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="338e11dd-9b15-475b-8471-fcb79439c886" xmlns:ns3="edfbc03d-db26-4301-8719-99148ee26221" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d69b3a9fc9dd1d280a5efa296263df02" ns2:_="" ns3:_="">
     <xsd:import namespace="338e11dd-9b15-475b-8471-fcb79439c886"/>
@@ -4768,7 +4734,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="edfbc03d-db26-4301-8719-99148ee26221">
@@ -4803,24 +4828,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A138CF7A-8662-4303-935C-7BE86E2888FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3691F1F7-72B1-41D9-8657-9C07AFE6AA73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4839,7 +4847,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A138CF7A-8662-4303-935C-7BE86E2888FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78F48322-4FD1-4D94-BEE5-6BE781D24505}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FA96AA6-3687-4803-9D38-8F86AB3B850C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -4854,12 +4878,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78F48322-4FD1-4D94-BEE5-6BE781D24505}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>